--- a/tudien.xlsx
+++ b/tudien.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D589"/>
+  <dimension ref="A1:D623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -13390,6 +13390,754 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>trai mit</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>trái mít</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>jackfruit</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>vai</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>vải</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>lici</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>trai vai</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>trái vải</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>lici</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>trai nhan</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>trái nhãn</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>longan</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>trai oi</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>trái ổi</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>guava</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>hong</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>hồng</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>kaki</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>qua hong</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>quả hồng</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>kaki</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>khe</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>khế</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>karambola</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>trai khe</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>trái khế</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>karambola</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>anona</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>mang cau</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>mãng cầu</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>anona</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>man cau</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>mãng cầu</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>anona</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>sung</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>sung</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>fiky</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>trai sung</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>trái sung</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>fiky</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>quat</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>quất</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>kumquat</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>tac</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>tắc</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>kumquat</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>du du</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>đu đủ</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>papaja</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>mo</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>mơ</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>merunky</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>cha la</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>chà là</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>datle</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>nam viet quat</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>nam việt quất</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>brusinky</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>dau</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>dâu</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>jahody</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>trai dau</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>trái dâu</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>jahody</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>dua gang</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>dưa gang</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>meloun</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>tamarind</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Trái cây</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>bang dinh</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>băng dính</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>paska</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>bang keo</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>băng keo</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>paska</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>bang dan</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>băng dán</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>paska</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>bang dinh trong</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>băng dính trong</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>lepici paska</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>bang keo dong goi</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>băng keo đóng gói</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>balici paska</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>bang keo hai mat</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>băng keo hai mặt</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>oboustranna paska</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>bang dinh hai mat</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>băng dính hai mặt</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>oboustranna paska</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>bang keo dien</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>băng keo điện</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>izolacni paska</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>bang dinh dien</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>băng dính điện</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>izolacni paska</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>bang keo giay</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>băng keo giấy</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>malirska paska</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Văn phòng/gia dụng</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
